--- a/Pure_English_Movie_Entertainment_Sentences_Final.xlsx
+++ b/Pure_English_Movie_Entertainment_Sentences_Final.xlsx
@@ -8305,7 +8305,7 @@
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="30" customHeight="1">
       <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
@@ -8375,7 +8375,7 @@
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="30" customHeight="1">
       <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
